--- a/data/fullyear-resilience/Power_BusInfo.xlsx
+++ b/data/fullyear-resilience/Power_BusInfo.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Simon Malacek\Code\LEGO-Pyomo\data\mini-example-resilience\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Simon Malacek\Code\LEGO-Pyomo\data\fullyear-resilience\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9BCDF0B-D9BF-4A3C-AE72-3CA8F48F8811}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EE15EBB-47A0-4D64-B86E-F0D6453AB816}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ScenarioA" sheetId="1" r:id="rId1"/>
+    <sheet name="year2017" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
@@ -113,8 +114,102 @@
 </comments>
 </file>
 
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author/>
+  </authors>
+  <commentList>
+    <comment ref="A3" authorId="0" shapeId="0" xr:uid="{20374A37-AC84-437C-BB0F-2648CF87E9D4}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>If a line has a value in this column, it is not read in (i.e., does not exist).</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B3" authorId="0" shapeId="0" xr:uid="{31191BC3-2A46-4CBB-BDA8-65A84802F9C4}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Readable name</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B4" authorId="0" shapeId="0" xr:uid="{ACCAA281-B607-4504-BF50-92B3BE9DBCA0}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Value specifier in database</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B5" authorId="0" shapeId="0" xr:uid="{6FAA2D93-DB3E-4288-9C37-F5BA7A6C37E8}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Description</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B6" authorId="0" shapeId="0" xr:uid="{9ECF2C78-8F86-4632-815F-26BA7CE826A7}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Details on database behavior</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B7" authorId="0" shapeId="0" xr:uid="{1197F74A-DAE6-42DD-907A-F7FDC237ABF1}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Unit or valid values</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="67">
   <si>
     <t>Power - Bus information</t>
   </si>
@@ -1296,4 +1391,538 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B918826D-EFB8-4D16-ABF9-FD984E3AD961}">
+  <sheetPr>
+    <tabColor rgb="FF008080"/>
+  </sheetPr>
+  <dimension ref="A1:Q16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="5.5703125" customWidth="1"/>
+    <col min="2" max="2" width="19.7109375" customWidth="1"/>
+    <col min="3" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="12" width="20.140625" customWidth="1"/>
+    <col min="13" max="14" width="15.7109375" customWidth="1"/>
+    <col min="15" max="15" width="18.7109375" customWidth="1"/>
+    <col min="16" max="17" width="24.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="1"/>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="L3" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="M3" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="N3" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="O3" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="P3" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q3" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A4" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="K4" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L4" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="M4" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="N4" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="O4" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="P4" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q4" s="6" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="7"/>
+      <c r="B5" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="J5" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="K5" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="L5" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="M5" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="N5" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="O5" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="P5" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q5" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="8"/>
+      <c r="B6" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="I6" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="J6" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="K6" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="L6" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="M6" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="N6" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="O6" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="P6" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q6" s="8" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A7" s="9"/>
+      <c r="B7" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="I7" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="J7" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="K7" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="L7" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="M7" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="N7" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="O7" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="P7" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q7" s="9" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A8" s="10"/>
+      <c r="B8" s="11"/>
+      <c r="C8" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="E8" s="13">
+        <v>220</v>
+      </c>
+      <c r="F8" s="14">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="G8" s="14">
+        <v>0.9</v>
+      </c>
+      <c r="H8" s="14">
+        <v>0</v>
+      </c>
+      <c r="I8" s="14">
+        <v>0</v>
+      </c>
+      <c r="J8" s="15">
+        <v>0.95</v>
+      </c>
+      <c r="K8" s="16">
+        <v>2000</v>
+      </c>
+      <c r="L8" s="16">
+        <v>2023</v>
+      </c>
+      <c r="M8" s="17">
+        <v>47.272599999999997</v>
+      </c>
+      <c r="N8" s="17">
+        <v>11.471399999999999</v>
+      </c>
+      <c r="O8" s="18">
+        <v>1</v>
+      </c>
+      <c r="P8" s="19"/>
+      <c r="Q8" s="19"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A9" s="10"/>
+      <c r="B9" s="11"/>
+      <c r="C9" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="D9" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="E9" s="13">
+        <v>220</v>
+      </c>
+      <c r="F9" s="14">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="G9" s="14">
+        <v>0.9</v>
+      </c>
+      <c r="H9" s="14">
+        <v>0</v>
+      </c>
+      <c r="I9" s="14">
+        <v>0</v>
+      </c>
+      <c r="J9" s="15">
+        <v>0.95</v>
+      </c>
+      <c r="K9" s="16">
+        <v>2000</v>
+      </c>
+      <c r="L9" s="16">
+        <v>2023</v>
+      </c>
+      <c r="M9" s="17">
+        <v>47.272599999999997</v>
+      </c>
+      <c r="N9" s="17">
+        <v>11.471399999999999</v>
+      </c>
+      <c r="O9" s="18">
+        <v>1</v>
+      </c>
+      <c r="P9" s="19"/>
+      <c r="Q9" s="19"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A10" s="10"/>
+      <c r="B10" s="11"/>
+      <c r="C10" s="12"/>
+      <c r="D10" s="12"/>
+      <c r="E10" s="13"/>
+      <c r="F10" s="14"/>
+      <c r="G10" s="14"/>
+      <c r="H10" s="14"/>
+      <c r="I10" s="14"/>
+      <c r="J10" s="15"/>
+      <c r="K10" s="16"/>
+      <c r="L10" s="16"/>
+      <c r="M10" s="17"/>
+      <c r="N10" s="17"/>
+      <c r="O10" s="18"/>
+      <c r="P10" s="19"/>
+      <c r="Q10" s="19"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A11" s="10"/>
+      <c r="B11" s="11"/>
+      <c r="C11" s="12"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="13"/>
+      <c r="F11" s="14"/>
+      <c r="G11" s="14"/>
+      <c r="H11" s="14"/>
+      <c r="I11" s="14"/>
+      <c r="J11" s="15"/>
+      <c r="K11" s="16"/>
+      <c r="L11" s="16"/>
+      <c r="M11" s="17"/>
+      <c r="N11" s="17"/>
+      <c r="O11" s="18"/>
+      <c r="P11" s="19"/>
+      <c r="Q11" s="19"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A12" s="10"/>
+      <c r="B12" s="11"/>
+      <c r="C12" s="12"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="13"/>
+      <c r="F12" s="14"/>
+      <c r="G12" s="14"/>
+      <c r="H12" s="14"/>
+      <c r="I12" s="14"/>
+      <c r="J12" s="15"/>
+      <c r="K12" s="16"/>
+      <c r="L12" s="16"/>
+      <c r="M12" s="17"/>
+      <c r="N12" s="17"/>
+      <c r="O12" s="18"/>
+      <c r="P12" s="19"/>
+      <c r="Q12" s="19"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A13" s="10"/>
+      <c r="B13" s="11"/>
+      <c r="C13" s="12"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="13"/>
+      <c r="F13" s="14"/>
+      <c r="G13" s="14"/>
+      <c r="H13" s="14"/>
+      <c r="I13" s="14"/>
+      <c r="J13" s="15"/>
+      <c r="K13" s="16"/>
+      <c r="L13" s="16"/>
+      <c r="M13" s="17"/>
+      <c r="N13" s="17"/>
+      <c r="O13" s="18"/>
+      <c r="P13" s="19"/>
+      <c r="Q13" s="19"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A14" s="10"/>
+      <c r="B14" s="11"/>
+      <c r="C14" s="12"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="13"/>
+      <c r="F14" s="14"/>
+      <c r="G14" s="14"/>
+      <c r="H14" s="14"/>
+      <c r="I14" s="14"/>
+      <c r="J14" s="15"/>
+      <c r="K14" s="16"/>
+      <c r="L14" s="16"/>
+      <c r="M14" s="17"/>
+      <c r="N14" s="17"/>
+      <c r="O14" s="18"/>
+      <c r="P14" s="19"/>
+      <c r="Q14" s="19"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A15" s="10"/>
+      <c r="B15" s="11"/>
+      <c r="C15" s="12"/>
+      <c r="D15" s="12"/>
+      <c r="E15" s="13"/>
+      <c r="F15" s="14"/>
+      <c r="G15" s="14"/>
+      <c r="H15" s="14"/>
+      <c r="I15" s="14"/>
+      <c r="J15" s="15"/>
+      <c r="K15" s="16"/>
+      <c r="L15" s="16"/>
+      <c r="M15" s="17"/>
+      <c r="N15" s="17"/>
+      <c r="O15" s="18"/>
+      <c r="P15" s="19"/>
+      <c r="Q15" s="19"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A16" s="10"/>
+      <c r="B16" s="11"/>
+      <c r="C16" s="12"/>
+      <c r="D16" s="12"/>
+      <c r="E16" s="13"/>
+      <c r="F16" s="14"/>
+      <c r="G16" s="14"/>
+      <c r="H16" s="14"/>
+      <c r="I16" s="14"/>
+      <c r="J16" s="15"/>
+      <c r="K16" s="16"/>
+      <c r="L16" s="16"/>
+      <c r="M16" s="17"/>
+      <c r="N16" s="17"/>
+      <c r="O16" s="18"/>
+      <c r="P16" s="19"/>
+      <c r="Q16" s="19"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
 </file>